--- a/request_off.xlsx
+++ b/request_off.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4d19684ef12fac30/바탕 화면/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="8_{FB5A5AD8-B37F-41F6-895D-0A7CCDD088EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CEB25EE-0E13-463C-856E-341A96F1156F}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="8_{FB5A5AD8-B37F-41F6-895D-0A7CCDD088EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BFEF992-EEA4-42E7-AC1C-CBE09913FC63}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{1D50B89D-8FBB-46C6-8B97-D810239EF683}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>김하나</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -126,10 +126,6 @@
   </si>
   <si>
     <t>장지윤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>O</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -630,10 +626,10 @@
   <sheetData>
     <row r="1" spans="1:34" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1" s="5">
         <v>1</v>
@@ -749,15 +745,9 @@
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
-      <c r="P2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
       <c r="S2" s="5"/>
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
@@ -786,54 +776,26 @@
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
-      <c r="G3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
       <c r="N3" s="5"/>
-      <c r="O3" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
-      <c r="U3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z3" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
       <c r="AA3" s="5"/>
       <c r="AB3" s="5"/>
       <c r="AC3" s="5"/>
@@ -867,9 +829,7 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
-      <c r="T4" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="T4" s="5"/>
       <c r="U4" s="5"/>
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
@@ -903,12 +863,8 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
-      <c r="N5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
@@ -936,12 +892,8 @@
       <c r="B6" s="5">
         <v>3</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -955,12 +907,8 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="S6" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
       <c r="V6" s="5"/>
@@ -999,21 +947,11 @@
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
-      <c r="R7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="T7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="U7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="V7" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
       <c r="Y7" s="5"/>
@@ -1042,12 +980,8 @@
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
-      <c r="K8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
@@ -1063,9 +997,7 @@
       <c r="Y8" s="5"/>
       <c r="Z8" s="5"/>
       <c r="AA8" s="5"/>
-      <c r="AB8" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="AB8" s="5"/>
       <c r="AC8" s="5"/>
       <c r="AD8" s="5"/>
       <c r="AE8" s="5"/>
@@ -1090,15 +1022,9 @@
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
-      <c r="M9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
@@ -1137,12 +1063,8 @@
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
@@ -1176,9 +1098,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
-      <c r="I11" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="I11" s="5"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
@@ -1186,9 +1106,7 @@
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
-      <c r="Q11" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
@@ -1214,15 +1132,9 @@
       <c r="B12" s="5">
         <v>2</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -1232,9 +1144,7 @@
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
-      <c r="O12" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="O12" s="5"/>
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
@@ -1277,9 +1187,7 @@
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
-      <c r="R13" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="R13" s="5"/>
       <c r="S13" s="5"/>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
@@ -1290,15 +1198,9 @@
       <c r="Z13" s="5"/>
       <c r="AA13" s="5"/>
       <c r="AB13" s="5"/>
-      <c r="AC13" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD13" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="AE13" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="AC13" s="5"/>
+      <c r="AD13" s="5"/>
+      <c r="AE13" s="5"/>
       <c r="AF13" s="5"/>
       <c r="AG13" s="5"/>
       <c r="AH13" s="2"/>
@@ -1310,9 +1212,7 @@
       <c r="B14" s="5">
         <v>2</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -1321,9 +1221,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
-      <c r="L14" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
@@ -1332,12 +1230,8 @@
       <c r="R14" s="5"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
-      <c r="U14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="V14" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
       <c r="Y14" s="5"/>
@@ -1384,12 +1278,8 @@
       <c r="Z15" s="5"/>
       <c r="AA15" s="5"/>
       <c r="AB15" s="5"/>
-      <c r="AC15" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD15" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="AC15" s="5"/>
+      <c r="AD15" s="5"/>
       <c r="AE15" s="5"/>
       <c r="AF15" s="5"/>
       <c r="AG15" s="5"/>
@@ -1482,15 +1372,9 @@
       <c r="B18" s="5">
         <v>1</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
@@ -1505,27 +1389,13 @@
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
       <c r="S18" s="5"/>
-      <c r="T18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="U18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="V18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="W18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="X18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z18" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5"/>
       <c r="AA18" s="5"/>
       <c r="AB18" s="5"/>
       <c r="AC18" s="5"/>
@@ -1542,9 +1412,7 @@
       <c r="B19" s="5">
         <v>1</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -1553,34 +1421,16 @@
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
-      <c r="L19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="N19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="O19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="R19" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
       <c r="S19" s="5"/>
-      <c r="T19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="U19" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
       <c r="V19" s="5"/>
       <c r="W19" s="5"/>
       <c r="X19" s="5"/>
@@ -1604,12 +1454,8 @@
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
-      <c r="E20" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
@@ -1622,18 +1468,12 @@
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
-      <c r="S20" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="T20" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
       <c r="U20" s="5"/>
       <c r="V20" s="5"/>
       <c r="W20" s="5"/>
-      <c r="X20" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="X20" s="5"/>
       <c r="Y20" s="5"/>
       <c r="Z20" s="5"/>
       <c r="AA20" s="5"/>
@@ -1692,12 +1532,8 @@
       <c r="B22" s="5">
         <v>1</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -1714,12 +1550,8 @@
       <c r="R22" s="5"/>
       <c r="S22" s="5"/>
       <c r="T22" s="5"/>
-      <c r="U22" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="V22" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
       <c r="W22" s="5"/>
       <c r="X22" s="5"/>
       <c r="Y22" s="5"/>
